--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/ALABAMA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/ALABAMA_2018.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C100">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C141">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C241">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C598">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C622">
